--- a/public/files/import_sales_template.xlsx
+++ b/public/files/import_sales_template.xlsx
@@ -4,46 +4,26 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="1">
     <font>
-      <name val="Arial"/>
-      <charset val="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <charset val="1"/>
-      <family val="1"/>
-      <sz val="10"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -63,39 +43,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -452,119 +409,166 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="11.52" customWidth="1" style="2" min="1" max="1025"/>
-  </cols>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="23.85" customHeight="1" s="3">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Invoice No.</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Customer Phone number</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Customer name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Customer Email</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Sale Date</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Product name</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Product SKU</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Product Unit</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Item Tax</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Item Discount</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Item Description</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Types of service</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Custom Field 1</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Custom Field 2</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Custom Field 3</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Custom Field 4</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>John Doe</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>john@example.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Test Product</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SKU001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pc</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="0">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/files/import_sales_template.xlsx
+++ b/public/files/import_sales_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,25 +484,40 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>Order Total</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Total Paid</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Payment Method</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Types of service</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Custom Field 1</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Custom Field 2</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Custom Field 3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Custom Field 4</t>
         </is>
@@ -562,11 +577,26 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
